--- a/Data/Results/System/TAT_Computation_Log.xlsx
+++ b/Data/Results/System/TAT_Computation_Log.xlsx
@@ -18,13 +18,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -35,7 +38,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -43,12 +46,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -418,12 +430,12 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Metric</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Value</t>
         </is>
@@ -448,7 +460,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>18</v>
+        <v>38</v>
       </c>
     </row>
     <row r="4">
@@ -458,7 +470,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>18</v>
+        <v>38</v>
       </c>
     </row>
     <row r="5">
@@ -516,56 +528,56 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J19"/>
+  <dimension ref="A1:J39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>pair_id</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>pair_workbook_path</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>status</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>ev_total_tat_min</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>ice_total_tat_min</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>ev_total_distance_km</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>ice_total_distance_km</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>ev_average_moving_speed_kmh</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>ice_average_moving_speed_kmh</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>error</t>
         </is>
@@ -579,7 +591,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>D:\TAT_MS_INTERCITY\Data\Results\Paired\15-07-2026\PAIR_001_STRICT_Chennai_to_Pondicherry.xlsx</t>
+          <t>D:\Hameeda_Projects\TAT_MS_INTERCITY\Data\Results\Paired\05-07-2026_to_29-07-2026\PAIR_001_NONSTRICT_SilkBoard_to_Madhuravoyal.xlsx</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,22 +600,22 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>240.4436333333333</v>
+        <v>98.16888333333333</v>
       </c>
       <c r="E2" t="n">
-        <v>274.35</v>
+        <v>85.5448</v>
       </c>
       <c r="F2" t="n">
-        <v>148.1987690237775</v>
+        <v>102.5403079815431</v>
       </c>
       <c r="G2" t="n">
-        <v>148.1254196841063</v>
+        <v>102.5404226319246</v>
       </c>
       <c r="H2" t="n">
-        <v>41.58535677727425</v>
+        <v>76.08025778994646</v>
       </c>
       <c r="I2" t="n">
-        <v>43.13601932523515</v>
+        <v>76.61984720324178</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -619,7 +631,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>D:\TAT_MS_INTERCITY\Data\Results\Paired\15-07-2026_to_17-07-2026\PAIR_002_NONSTRICT_Chennai_to_Pondicherry.xlsx</t>
+          <t>D:\Hameeda_Projects\TAT_MS_INTERCITY\Data\Results\Paired\05-07-2026_to_05-09-2026\PAIR_002_NONSTRICT_SilkBoard_to_Madhuravoyal.xlsx</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -628,22 +640,22 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>209.5919166666667</v>
+        <v>25.27086666666667</v>
       </c>
       <c r="E3" t="n">
-        <v>221.15</v>
+        <v>20.34321666666666</v>
       </c>
       <c r="F3" t="n">
-        <v>141.62200313376</v>
+        <v>27.18076401749682</v>
       </c>
       <c r="G3" t="n">
-        <v>141.6711046862772</v>
+        <v>27.2938636578444</v>
       </c>
       <c r="H3" t="n">
-        <v>46.13817614056148</v>
+        <v>72.17266749628908</v>
       </c>
       <c r="I3" t="n">
-        <v>44.82161408578494</v>
+        <v>80.50014146258407</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -659,7 +671,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>D:\TAT_MS_INTERCITY\Data\Results\Paired\15-07-2026_to_17-07-2026\PAIR_003_NONSTRICT_Chennai_to_Pondicherry.xlsx</t>
+          <t>D:\Hameeda_Projects\TAT_MS_INTERCITY\Data\Results\Paired\10-07-2026_to_31-07-2026\PAIR_003_NONSTRICT_Madhuravoyal_to_SilkBoard.xlsx</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -668,22 +680,22 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>221.5170833333333</v>
+        <v>18.67793333333333</v>
       </c>
       <c r="E4" t="n">
-        <v>274.35</v>
+        <v>29.6565</v>
       </c>
       <c r="F4" t="n">
-        <v>148.208411945328</v>
+        <v>11.42391390088974</v>
       </c>
       <c r="G4" t="n">
-        <v>148.150219573912</v>
+        <v>11.63657856259103</v>
       </c>
       <c r="H4" t="n">
-        <v>46.35627936949886</v>
+        <v>55.44692920604529</v>
       </c>
       <c r="I4" t="n">
-        <v>43.14328255361949</v>
+        <v>59.58783215117909</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -699,7 +711,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>D:\TAT_MS_INTERCITY\Data\Results\Paired\15-07-2026_to_19-07-2026\PAIR_004_NONSTRICT_Chennai_to_Pondicherry.xlsx</t>
+          <t>D:\Hameeda_Projects\TAT_MS_INTERCITY\Data\Results\Paired\15-07-2026\PAIR_004_STRICT_Chennai_to_Pondicherry.xlsx</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -708,22 +720,22 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>232.8915666666666</v>
+        <v>240.4436333333333</v>
       </c>
       <c r="E5" t="n">
-        <v>269.2166666666666</v>
+        <v>274.35</v>
       </c>
       <c r="F5" t="n">
-        <v>146.1103622297162</v>
+        <v>148.1987690237775</v>
       </c>
       <c r="G5" t="n">
-        <v>146.1941703909393</v>
+        <v>148.1254196841063</v>
       </c>
       <c r="H5" t="n">
-        <v>43.31882927503337</v>
+        <v>42.80810564129094</v>
       </c>
       <c r="I5" t="n">
-        <v>44.09960930384722</v>
+        <v>44.7845362014835</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -739,7 +751,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>D:\TAT_MS_INTERCITY\Data\Results\Paired\15-07-2026_to_19-07-2026\PAIR_005_NONSTRICT_Chennai_to_Pondicherry.xlsx</t>
+          <t>D:\Hameeda_Projects\TAT_MS_INTERCITY\Data\Results\Paired\15-07-2026_to_17-07-2026\PAIR_005_NONSTRICT_Chennai_to_Pondicherry.xlsx</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -748,22 +760,22 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>199.7801333333333</v>
+        <v>209.5919166666667</v>
       </c>
       <c r="E6" t="n">
-        <v>272.7087666666667</v>
+        <v>221.15</v>
       </c>
       <c r="F6" t="n">
-        <v>147.8063808897662</v>
+        <v>141.62200313376</v>
       </c>
       <c r="G6" t="n">
-        <v>147.7347082243865</v>
+        <v>141.6711046862772</v>
       </c>
       <c r="H6" t="n">
-        <v>47.1164527446597</v>
+        <v>47.25384199133067</v>
       </c>
       <c r="I6" t="n">
-        <v>43.36902945799262</v>
+        <v>44.82161408578494</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
@@ -779,7 +791,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>D:\TAT_MS_INTERCITY\Data\Results\Paired\16-07-2026\PAIR_006_STRICT_Pondicherry_to_Chennai.xlsx</t>
+          <t>D:\Hameeda_Projects\TAT_MS_INTERCITY\Data\Results\Paired\15-07-2026_to_17-07-2026\PAIR_006_NONSTRICT_Chennai_to_Pondicherry.xlsx</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -788,22 +800,22 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>241.37365</v>
+        <v>221.5170833333333</v>
       </c>
       <c r="E7" t="n">
-        <v>241.6157666666667</v>
+        <v>274.35</v>
       </c>
       <c r="F7" t="n">
-        <v>143.678327457659</v>
+        <v>148.208411945328</v>
       </c>
       <c r="G7" t="n">
-        <v>143.7061031155876</v>
+        <v>148.150219573912</v>
       </c>
       <c r="H7" t="n">
-        <v>43.15630919960726</v>
+        <v>49.30661820086556</v>
       </c>
       <c r="I7" t="n">
-        <v>42.008597388821</v>
+        <v>44.79217019920052</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
@@ -819,7 +831,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>D:\TAT_MS_INTERCITY\Data\Results\Paired\16-07-2026_to_18-07-2026\PAIR_007_NONSTRICT_Pondicherry_to_Chennai.xlsx</t>
+          <t>D:\Hameeda_Projects\TAT_MS_INTERCITY\Data\Results\Paired\15-07-2026_to_19-07-2026\PAIR_007_NONSTRICT_Chennai_to_Pondicherry.xlsx</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -828,22 +840,22 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>171.54615</v>
+        <v>232.8915666666666</v>
       </c>
       <c r="E8" t="n">
-        <v>188.0674333333333</v>
+        <v>269.2166666666666</v>
       </c>
       <c r="F8" t="n">
-        <v>126.503272181271</v>
+        <v>146.1103622297162</v>
       </c>
       <c r="G8" t="n">
-        <v>126.4504264596244</v>
+        <v>146.1941703909393</v>
       </c>
       <c r="H8" t="n">
-        <v>51.80910898442515</v>
+        <v>44.76153869689547</v>
       </c>
       <c r="I8" t="n">
-        <v>46.12090225545156</v>
+        <v>44.84902776787012</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
@@ -859,7 +871,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>D:\TAT_MS_INTERCITY\Data\Results\Paired\16-07-2026_to_18-07-2026\PAIR_008_NONSTRICT_Pondicherry_to_Chennai.xlsx</t>
+          <t>D:\Hameeda_Projects\TAT_MS_INTERCITY\Data\Results\Paired\15-07-2026_to_19-07-2026\PAIR_008_NONSTRICT_Chennai_to_Pondicherry.xlsx</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -868,22 +880,22 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>183.89555</v>
+        <v>199.7801333333333</v>
       </c>
       <c r="E9" t="n">
-        <v>180.3055833333333</v>
+        <v>272.7087666666667</v>
       </c>
       <c r="F9" t="n">
-        <v>126.6046070482763</v>
+        <v>147.8063808897662</v>
       </c>
       <c r="G9" t="n">
-        <v>126.5641866441461</v>
+        <v>147.7347082243865</v>
       </c>
       <c r="H9" t="n">
-        <v>46.70774678068461</v>
+        <v>48.10943109063845</v>
       </c>
       <c r="I9" t="n">
-        <v>49.76956595619203</v>
+        <v>45.04354059322232</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
@@ -899,7 +911,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>D:\TAT_MS_INTERCITY\Data\Results\Paired\16-07-2026_to_20-07-2026\PAIR_009_NONSTRICT_Pondicherry_to_Chennai.xlsx</t>
+          <t>D:\Hameeda_Projects\TAT_MS_INTERCITY\Data\Results\Paired\15-07-2026_to_25-09-2026\PAIR_009_NONSTRICT_Chennai_to_Pondicherry.xlsx</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -908,22 +920,22 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>205.7538833333333</v>
+        <v>247.26765</v>
       </c>
       <c r="E10" t="n">
-        <v>194.9584</v>
+        <v>274.35</v>
       </c>
       <c r="F10" t="n">
-        <v>123.9185956857711</v>
+        <v>148.4081122812309</v>
       </c>
       <c r="G10" t="n">
-        <v>123.941936072907</v>
+        <v>148.1693420519742</v>
       </c>
       <c r="H10" t="n">
-        <v>43.25878919401418</v>
+        <v>47.63775321159345</v>
       </c>
       <c r="I10" t="n">
-        <v>42.80552488152868</v>
+        <v>44.79805655414056</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
@@ -939,7 +951,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>D:\TAT_MS_INTERCITY\Data\Results\Paired\16-07-2026_to_20-07-2026\PAIR_010_NONSTRICT_Pondicherry_to_Chennai.xlsx</t>
+          <t>D:\Hameeda_Projects\TAT_MS_INTERCITY\Data\Results\Paired\16-07-2026\PAIR_010_STRICT_Pondicherry_to_Chennai.xlsx</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -948,22 +960,22 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>223.0419833333333</v>
+        <v>241.37365</v>
       </c>
       <c r="E11" t="n">
         <v>241.6157666666667</v>
       </c>
       <c r="F11" t="n">
-        <v>143.715559613142</v>
+        <v>143.678327457659</v>
       </c>
       <c r="G11" t="n">
-        <v>143.7030109884508</v>
+        <v>143.7061031155876</v>
       </c>
       <c r="H11" t="n">
-        <v>45.56809333466344</v>
+        <v>44.63387255371435</v>
       </c>
       <c r="I11" t="n">
-        <v>42.0076907503904</v>
+        <v>42.34188357413701</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
@@ -979,7 +991,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>D:\TAT_MS_INTERCITY\Data\Results\Paired\17-07-2026\PAIR_011_STRICT_Chennai_to_Pondicherry.xlsx</t>
+          <t>D:\Hameeda_Projects\TAT_MS_INTERCITY\Data\Results\Paired\16-07-2026_to_18-07-2026\PAIR_011_NONSTRICT_Pondicherry_to_Chennai.xlsx</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -988,22 +1000,22 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>205.6434166666667</v>
+        <v>171.54615</v>
       </c>
       <c r="E12" t="n">
-        <v>221.15</v>
+        <v>188.0674333333333</v>
       </c>
       <c r="F12" t="n">
-        <v>141.5990549680233</v>
+        <v>126.503272181271</v>
       </c>
       <c r="G12" t="n">
-        <v>141.6663057069586</v>
+        <v>126.4504264596244</v>
       </c>
       <c r="H12" t="n">
-        <v>48.28995397818726</v>
+        <v>51.96681218238075</v>
       </c>
       <c r="I12" t="n">
-        <v>44.82009341634151</v>
+        <v>46.52364975832732</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
@@ -1019,7 +1031,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>D:\TAT_MS_INTERCITY\Data\Results\Paired\17-07-2026_to_19-07-2026\PAIR_012_NONSTRICT_Chennai_to_Pondicherry.xlsx</t>
+          <t>D:\Hameeda_Projects\TAT_MS_INTERCITY\Data\Results\Paired\16-07-2026_to_18-07-2026\PAIR_012_NONSTRICT_Pondicherry_to_Chennai.xlsx</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1028,22 +1040,22 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>219.9365833333333</v>
+        <v>183.89555</v>
       </c>
       <c r="E13" t="n">
-        <v>269.2166666666666</v>
+        <v>180.3055833333333</v>
       </c>
       <c r="F13" t="n">
-        <v>146.1177802267258</v>
+        <v>126.6046070482763</v>
       </c>
       <c r="G13" t="n">
-        <v>146.2265476173816</v>
+        <v>126.5641866441461</v>
       </c>
       <c r="H13" t="n">
-        <v>46.08133386225383</v>
+        <v>48.84353918109128</v>
       </c>
       <c r="I13" t="n">
-        <v>44.10804715430679</v>
+        <v>49.97551623726486</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -1059,7 +1071,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>D:\TAT_MS_INTERCITY\Data\Results\Paired\17-07-2026_to_19-07-2026\PAIR_013_NONSTRICT_Chennai_to_Pondicherry.xlsx</t>
+          <t>D:\Hameeda_Projects\TAT_MS_INTERCITY\Data\Results\Paired\16-07-2026_to_20-07-2026\PAIR_013_NONSTRICT_Pondicherry_to_Chennai.xlsx</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1068,22 +1080,22 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>186.11555</v>
+        <v>205.7538833333333</v>
       </c>
       <c r="E14" t="n">
-        <v>221.15</v>
+        <v>194.9584</v>
       </c>
       <c r="F14" t="n">
-        <v>141.7178099447946</v>
+        <v>123.9185956857711</v>
       </c>
       <c r="G14" t="n">
-        <v>141.7137294264382</v>
+        <v>123.941936072907</v>
       </c>
       <c r="H14" t="n">
-        <v>47.90276473827162</v>
+        <v>44.92387297676966</v>
       </c>
       <c r="I14" t="n">
-        <v>44.83512073701105</v>
+        <v>42.76203218085404</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
@@ -1099,7 +1111,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>D:\TAT_MS_INTERCITY\Data\Results\Paired\18-07-2026\PAIR_014_STRICT_Pondicherry_to_Chennai.xlsx</t>
+          <t>D:\Hameeda_Projects\TAT_MS_INTERCITY\Data\Results\Paired\16-07-2026_to_20-07-2026\PAIR_014_NONSTRICT_Pondicherry_to_Chennai.xlsx</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1108,22 +1120,22 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>184.8726166666667</v>
+        <v>223.0419833333333</v>
       </c>
       <c r="E15" t="n">
-        <v>189.8237333333333</v>
+        <v>241.6157666666667</v>
       </c>
       <c r="F15" t="n">
-        <v>126.797111280885</v>
+        <v>143.715559613142</v>
       </c>
       <c r="G15" t="n">
-        <v>126.7676219192398</v>
+        <v>143.7030109884508</v>
       </c>
       <c r="H15" t="n">
-        <v>46.49901997986691</v>
+        <v>46.2946098216972</v>
       </c>
       <c r="I15" t="n">
-        <v>45.74782714011837</v>
+        <v>42.3414520907443</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
@@ -1139,7 +1151,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>D:\TAT_MS_INTERCITY\Data\Results\Paired\18-07-2026_to_20-07-2026\PAIR_015_NONSTRICT_Pondicherry_to_Chennai.xlsx</t>
+          <t>D:\Hameeda_Projects\TAT_MS_INTERCITY\Data\Results\Paired\16-07-2026_to_26-09-2026\PAIR_015_NONSTRICT_Pondicherry_to_Chennai.xlsx</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1148,22 +1160,22 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>139.3205333333333</v>
+        <v>72.03223333333334</v>
       </c>
       <c r="E16" t="n">
-        <v>149.51085</v>
+        <v>78.34408333333334</v>
       </c>
       <c r="F16" t="n">
-        <v>106.7510397234517</v>
+        <v>44.14952488525887</v>
       </c>
       <c r="G16" t="n">
-        <v>106.7303536725813</v>
+        <v>44.09816148211158</v>
       </c>
       <c r="H16" t="n">
-        <v>51.59099322590557</v>
+        <v>49.19356496670422</v>
       </c>
       <c r="I16" t="n">
-        <v>49.9289852595555</v>
+        <v>48.98583197131639</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
@@ -1179,7 +1191,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>D:\TAT_MS_INTERCITY\Data\Results\Paired\18-07-2026_to_20-07-2026\PAIR_016_NONSTRICT_Pondicherry_to_Chennai.xlsx</t>
+          <t>D:\Hameeda_Projects\TAT_MS_INTERCITY\Data\Results\Paired\17-07-2026\PAIR_016_STRICT_Chennai_to_Pondicherry.xlsx</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1188,22 +1200,22 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>166.3452166666667</v>
+        <v>205.6434166666667</v>
       </c>
       <c r="E17" t="n">
-        <v>188.0674333333333</v>
+        <v>221.15</v>
       </c>
       <c r="F17" t="n">
-        <v>126.5111630773044</v>
+        <v>141.5990549680233</v>
       </c>
       <c r="G17" t="n">
-        <v>126.4609732010443</v>
+        <v>141.6663057069586</v>
       </c>
       <c r="H17" t="n">
-        <v>53.18742578062445</v>
+        <v>51.08928882117495</v>
       </c>
       <c r="I17" t="n">
-        <v>46.12475258422111</v>
+        <v>44.82009341634151</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
@@ -1219,7 +1231,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>D:\TAT_MS_INTERCITY\Data\Results\Paired\19-07-2026\PAIR_017_STRICT_Chennai_to_Pondicherry.xlsx</t>
+          <t>D:\Hameeda_Projects\TAT_MS_INTERCITY\Data\Results\Paired\17-07-2026_to_19-07-2026\PAIR_017_NONSTRICT_Chennai_to_Pondicherry.xlsx</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1228,22 +1240,22 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>195.4022</v>
+        <v>219.9365833333333</v>
       </c>
       <c r="E18" t="n">
-        <v>266.8632166666667</v>
+        <v>269.2166666666666</v>
       </c>
       <c r="F18" t="n">
-        <v>145.9064422742808</v>
+        <v>146.1177802267258</v>
       </c>
       <c r="G18" t="n">
-        <v>145.9943306994593</v>
+        <v>146.2265476173816</v>
       </c>
       <c r="H18" t="n">
-        <v>46.86485275946674</v>
+        <v>48.97751792605069</v>
       </c>
       <c r="I18" t="n">
-        <v>44.5741238531821</v>
+        <v>44.8576416936978</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
@@ -1259,7 +1271,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>D:\TAT_MS_INTERCITY\Data\Results\Paired\20-07-2026\PAIR_018_STRICT_Pondicherry_to_Chennai.xlsx</t>
+          <t>D:\Hameeda_Projects\TAT_MS_INTERCITY\Data\Results\Paired\17-07-2026_to_19-07-2026\PAIR_018_NONSTRICT_Chennai_to_Pondicherry.xlsx</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1268,24 +1280,824 @@
         </is>
       </c>
       <c r="D19" t="n">
+        <v>186.11555</v>
+      </c>
+      <c r="E19" t="n">
+        <v>221.15</v>
+      </c>
+      <c r="F19" t="n">
+        <v>141.7178099447946</v>
+      </c>
+      <c r="G19" t="n">
+        <v>141.7137294264382</v>
+      </c>
+      <c r="H19" t="n">
+        <v>48.97984764694002</v>
+      </c>
+      <c r="I19" t="n">
+        <v>44.83512073701105</v>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>PAIR_019</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>D:\Hameeda_Projects\TAT_MS_INTERCITY\Data\Results\Paired\17-07-2026_to_25-09-2026\PAIR_019_NONSTRICT_Chennai_to_Pondicherry.xlsx</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>221.1224333333333</v>
+      </c>
+      <c r="E20" t="n">
+        <v>221.15</v>
+      </c>
+      <c r="F20" t="n">
+        <v>141.8317368861638</v>
+      </c>
+      <c r="G20" t="n">
+        <v>141.6733980516045</v>
+      </c>
+      <c r="H20" t="n">
+        <v>49.27030586470386</v>
+      </c>
+      <c r="I20" t="n">
+        <v>44.82234079251659</v>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>PAIR_020</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>D:\Hameeda_Projects\TAT_MS_INTERCITY\Data\Results\Paired\18-07-2026\PAIR_020_STRICT_Pondicherry_to_Chennai.xlsx</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>184.8726166666667</v>
+      </c>
+      <c r="E21" t="n">
+        <v>189.8237333333333</v>
+      </c>
+      <c r="F21" t="n">
+        <v>126.797111280885</v>
+      </c>
+      <c r="G21" t="n">
+        <v>126.7676219192398</v>
+      </c>
+      <c r="H21" t="n">
+        <v>48.60919773277766</v>
+      </c>
+      <c r="I21" t="n">
+        <v>46.13403705248899</v>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>PAIR_021</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>D:\Hameeda_Projects\TAT_MS_INTERCITY\Data\Results\Paired\18-07-2026_to_20-07-2026\PAIR_021_NONSTRICT_Pondicherry_to_Chennai.xlsx</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>139.3205333333333</v>
+      </c>
+      <c r="E22" t="n">
+        <v>149.51085</v>
+      </c>
+      <c r="F22" t="n">
+        <v>106.7510397234517</v>
+      </c>
+      <c r="G22" t="n">
+        <v>106.7303536725813</v>
+      </c>
+      <c r="H22" t="n">
+        <v>51.58938782842431</v>
+      </c>
+      <c r="I22" t="n">
+        <v>49.91426587048593</v>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>PAIR_022</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>D:\Hameeda_Projects\TAT_MS_INTERCITY\Data\Results\Paired\18-07-2026_to_20-07-2026\PAIR_022_NONSTRICT_Pondicherry_to_Chennai.xlsx</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>166.3452166666667</v>
+      </c>
+      <c r="E23" t="n">
+        <v>188.0674333333333</v>
+      </c>
+      <c r="F23" t="n">
+        <v>126.5111630773044</v>
+      </c>
+      <c r="G23" t="n">
+        <v>126.4609732010443</v>
+      </c>
+      <c r="H23" t="n">
+        <v>54.3571101011709</v>
+      </c>
+      <c r="I23" t="n">
+        <v>46.52817854574852</v>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>PAIR_023</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>D:\Hameeda_Projects\TAT_MS_INTERCITY\Data\Results\Paired\18-07-2026_to_26-09-2026\PAIR_023_NONSTRICT_Pondicherry_to_Chennai.xlsx</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>72.03223333333334</v>
+      </c>
+      <c r="E24" t="n">
+        <v>81.07328333333334</v>
+      </c>
+      <c r="F24" t="n">
+        <v>44.14425672881129</v>
+      </c>
+      <c r="G24" t="n">
+        <v>44.07790624114242</v>
+      </c>
+      <c r="H24" t="n">
+        <v>49.18766031137466</v>
+      </c>
+      <c r="I24" t="n">
+        <v>46.38866788428458</v>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>PAIR_024</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>D:\Hameeda_Projects\TAT_MS_INTERCITY\Data\Results\Paired\19-07-2026\PAIR_024_STRICT_Chennai_to_Pondicherry.xlsx</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>195.4022</v>
+      </c>
+      <c r="E25" t="n">
+        <v>266.8632166666667</v>
+      </c>
+      <c r="F25" t="n">
+        <v>145.9064422742808</v>
+      </c>
+      <c r="G25" t="n">
+        <v>145.9943306994593</v>
+      </c>
+      <c r="H25" t="n">
+        <v>48.03268705989514</v>
+      </c>
+      <c r="I25" t="n">
+        <v>45.34276468747346</v>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>PAIR_025</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>D:\Hameeda_Projects\TAT_MS_INTERCITY\Data\Results\Paired\19-07-2026_to_25-09-2026\PAIR_025_NONSTRICT_Chennai_to_Pondicherry.xlsx</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>255.7438833333333</v>
+      </c>
+      <c r="E26" t="n">
+        <v>265.6299833333333</v>
+      </c>
+      <c r="F26" t="n">
+        <v>145.9773325040056</v>
+      </c>
+      <c r="G26" t="n">
+        <v>145.8893363990339</v>
+      </c>
+      <c r="H26" t="n">
+        <v>47.2452299004206</v>
+      </c>
+      <c r="I26" t="n">
+        <v>45.59497163487288</v>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>PAIR_026</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>D:\Hameeda_Projects\TAT_MS_INTERCITY\Data\Results\Paired\20-07-2026\PAIR_026_STRICT_Pondicherry_to_Chennai.xlsx</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
         <v>187.65295</v>
       </c>
-      <c r="E19" t="n">
+      <c r="E27" t="n">
         <v>194.9584</v>
       </c>
-      <c r="F19" t="n">
+      <c r="F27" t="n">
         <v>123.9926446469637</v>
       </c>
-      <c r="G19" t="n">
+      <c r="G27" t="n">
         <v>123.9802750677086</v>
       </c>
-      <c r="H19" t="n">
-        <v>46.87226586428536</v>
-      </c>
-      <c r="I19" t="n">
-        <v>42.81877758960633</v>
-      </c>
-      <c r="J19" t="inlineStr">
+      <c r="H27" t="n">
+        <v>46.88285886366883</v>
+      </c>
+      <c r="I27" t="n">
+        <v>42.76169445348732</v>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>PAIR_027</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>D:\Hameeda_Projects\TAT_MS_INTERCITY\Data\Results\Paired\20-07-2026_to_29-07-2026\PAIR_027_NONSTRICT_SilkBoard_to_Madhuravoyal.xlsx</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>39.97585</v>
+      </c>
+      <c r="E28" t="n">
+        <v>23.74308333333333</v>
+      </c>
+      <c r="F28" t="n">
+        <v>14.82892455320712</v>
+      </c>
+      <c r="G28" t="n">
+        <v>15.14287648205564</v>
+      </c>
+      <c r="H28" t="n">
+        <v>57.87321624947242</v>
+      </c>
+      <c r="I28" t="n">
+        <v>38.26683233039817</v>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>PAIR_028</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>D:\Hameeda_Projects\TAT_MS_INTERCITY\Data\Results\Paired\20-07-2026_to_05-09-2026\PAIR_028_NONSTRICT_SilkBoard_to_Madhuravoyal.xlsx</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>20.26271666666667</v>
+      </c>
+      <c r="E29" t="n">
+        <v>19.8356</v>
+      </c>
+      <c r="F29" t="n">
+        <v>22.49736924506911</v>
+      </c>
+      <c r="G29" t="n">
+        <v>22.45363674285612</v>
+      </c>
+      <c r="H29" t="n">
+        <v>71.17338391598146</v>
+      </c>
+      <c r="I29" t="n">
+        <v>67.91920610273282</v>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>PAIR_029</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>D:\Hameeda_Projects\TAT_MS_INTERCITY\Data\Results\Paired\20-07-2026_to_26-09-2026\PAIR_029_NONSTRICT_Pondicherry_to_Chennai.xlsx</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>42.85905</v>
+      </c>
+      <c r="E30" t="n">
+        <v>45.4903</v>
+      </c>
+      <c r="F30" t="n">
+        <v>34.43958194459641</v>
+      </c>
+      <c r="G30" t="n">
+        <v>34.32677600023323</v>
+      </c>
+      <c r="H30" t="n">
+        <v>49.88240215190034</v>
+      </c>
+      <c r="I30" t="n">
+        <v>45.25609711599014</v>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>PAIR_030</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>D:\Hameeda_Projects\TAT_MS_INTERCITY\Data\Results\Paired\29-07-2026_to_06-09-2026\PAIR_030_NONSTRICT_SilkBoard_to_Madhuravoyal.xlsx</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>231.7772166666667</v>
+      </c>
+      <c r="E31" t="n">
+        <v>213.89885</v>
+      </c>
+      <c r="F31" t="n">
+        <v>231.4242273523428</v>
+      </c>
+      <c r="G31" t="n">
+        <v>231.3323956071126</v>
+      </c>
+      <c r="H31" t="n">
+        <v>67.59910743007244</v>
+      </c>
+      <c r="I31" t="n">
+        <v>70.84744357406082</v>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>PAIR_031</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>D:\Hameeda_Projects\TAT_MS_INTERCITY\Data\Results\Paired\31-07-2026_to_04-09-2026\PAIR_031_NONSTRICT_Madhuravoyal_to_SilkBoard.xlsx</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>14.8788</v>
+      </c>
+      <c r="E32" t="n">
+        <v>16.75645</v>
+      </c>
+      <c r="F32" t="n">
+        <v>12.73848083938423</v>
+      </c>
+      <c r="G32" t="n">
+        <v>12.6496249595659</v>
+      </c>
+      <c r="H32" t="n">
+        <v>51.36898475435208</v>
+      </c>
+      <c r="I32" t="n">
+        <v>45.29464758788131</v>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>PAIR_032</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>D:\Hameeda_Projects\TAT_MS_INTERCITY\Data\Results\Paired\05-09-2026_to_06-09-2026\PAIR_032_STRICT_SilkBoard_to_Madhuravoyal.xlsx</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>251.8893</v>
+      </c>
+      <c r="E33" t="n">
+        <v>234.6249833333333</v>
+      </c>
+      <c r="F33" t="n">
+        <v>240.4425765887812</v>
+      </c>
+      <c r="G33" t="n">
+        <v>240.7230050078111</v>
+      </c>
+      <c r="H33" t="n">
+        <v>64.24069875201077</v>
+      </c>
+      <c r="I33" t="n">
+        <v>68.13871680530009</v>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>PAIR_033</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>D:\Hameeda_Projects\TAT_MS_INTERCITY\Data\Results\Paired\11-09-2026\PAIR_033_STRICT_Madhuravoyal_to_Madiwala.xlsx</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>184.8808833333333</v>
+      </c>
+      <c r="E34" t="n">
+        <v>189.0966166666667</v>
+      </c>
+      <c r="F34" t="n">
+        <v>159.8172074707595</v>
+      </c>
+      <c r="G34" t="n">
+        <v>159.58380997156</v>
+      </c>
+      <c r="H34" t="n">
+        <v>58.20216621959079</v>
+      </c>
+      <c r="I34" t="n">
+        <v>55.92805804691302</v>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>PAIR_034</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>D:\Hameeda_Projects\TAT_MS_INTERCITY\Data\Results\Paired\11-09-2026_to_18-09-2026\PAIR_034_NONSTRICT_Madhuravoyal_to_Madiwala.xlsx</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>66.01939999999999</v>
+      </c>
+      <c r="E35" t="n">
+        <v>94.14933333333333</v>
+      </c>
+      <c r="F35" t="n">
+        <v>49.09342708546251</v>
+      </c>
+      <c r="G35" t="n">
+        <v>49.01363547616007</v>
+      </c>
+      <c r="H35" t="n">
+        <v>47.58550177729312</v>
+      </c>
+      <c r="I35" t="n">
+        <v>37.18511343393678</v>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>PAIR_035</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>D:\Hameeda_Projects\TAT_MS_INTERCITY\Data\Results\Paired\12-09-2026\PAIR_035_STRICT_Madiwala_to_Madhuravoyal.xlsx</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>13.15565</v>
+      </c>
+      <c r="E36" t="n">
+        <v>14.03436666666667</v>
+      </c>
+      <c r="F36" t="n">
+        <v>17.5104260598227</v>
+      </c>
+      <c r="G36" t="n">
+        <v>17.59592292311513</v>
+      </c>
+      <c r="H36" t="n">
+        <v>79.86116714790693</v>
+      </c>
+      <c r="I36" t="n">
+        <v>75.22643525442838</v>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>PAIR_036</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>D:\Hameeda_Projects\TAT_MS_INTERCITY\Data\Results\Paired\12-09-2026_to_20-09-2026\PAIR_036_NONSTRICT_Madiwala_to_Madhuravoyal.xlsx</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>11.71183333333333</v>
+      </c>
+      <c r="E37" t="n">
+        <v>11.73173333333333</v>
+      </c>
+      <c r="F37" t="n">
+        <v>16.43424965629278</v>
+      </c>
+      <c r="G37" t="n">
+        <v>16.43868693033036</v>
+      </c>
+      <c r="H37" t="n">
+        <v>84.19305084978724</v>
+      </c>
+      <c r="I37" t="n">
+        <v>84.07293174806406</v>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>PAIR_037</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>D:\Hameeda_Projects\TAT_MS_INTERCITY\Data\Results\Paired\12-09-2026_to_20-09-2026\PAIR_037_NONSTRICT_Madiwala_to_Madhuravoyal.xlsx</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>116.7043666666667</v>
+      </c>
+      <c r="E38" t="n">
+        <v>117.7956</v>
+      </c>
+      <c r="F38" t="n">
+        <v>106.4407237351212</v>
+      </c>
+      <c r="G38" t="n">
+        <v>106.429493371315</v>
+      </c>
+      <c r="H38" t="n">
+        <v>57.74313792935574</v>
+      </c>
+      <c r="I38" t="n">
+        <v>61.22560386453947</v>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>PAIR_038</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>D:\Hameeda_Projects\TAT_MS_INTERCITY\Data\Results\Paired\20-09-2026\PAIR_038_STRICT_Madiwala_to_Madhuravoyal.xlsx</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>154.2935833333334</v>
+      </c>
+      <c r="E39" t="n">
+        <v>89.89455</v>
+      </c>
+      <c r="F39" t="n">
+        <v>118.6528555237152</v>
+      </c>
+      <c r="G39" t="n">
+        <v>118.3205529638225</v>
+      </c>
+      <c r="H39" t="n">
+        <v>76.62526023529979</v>
+      </c>
+      <c r="I39" t="n">
+        <v>78.97289855535573</v>
+      </c>
+      <c r="J39" t="inlineStr">
         <is>
           <t>NONE</t>
         </is>

--- a/Data/Results/System/TAT_Computation_Log.xlsx
+++ b/Data/Results/System/TAT_Computation_Log.xlsx
@@ -460,7 +460,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>38</v>
+        <v>54</v>
       </c>
     </row>
     <row r="4">
@@ -470,7 +470,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>38</v>
+        <v>54</v>
       </c>
     </row>
     <row r="5">
@@ -528,7 +528,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J39"/>
+  <dimension ref="A1:J55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -600,22 +600,22 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>98.16888333333333</v>
+        <v>343.8404</v>
       </c>
       <c r="E2" t="n">
-        <v>85.5448</v>
+        <v>311.5075166666667</v>
       </c>
       <c r="F2" t="n">
-        <v>102.5403079815431</v>
+        <v>305.1665869122799</v>
       </c>
       <c r="G2" t="n">
-        <v>102.5404226319246</v>
+        <v>310.4742418277487</v>
       </c>
       <c r="H2" t="n">
-        <v>76.08025778994646</v>
+        <v>69.11154120244322</v>
       </c>
       <c r="I2" t="n">
-        <v>76.61984720324178</v>
+        <v>63.46076786637193</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -640,22 +640,22 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>25.27086666666667</v>
+        <v>343.8404</v>
       </c>
       <c r="E3" t="n">
-        <v>20.34321666666666</v>
+        <v>299.0182166666667</v>
       </c>
       <c r="F3" t="n">
-        <v>27.18076401749682</v>
+        <v>305.1072776594863</v>
       </c>
       <c r="G3" t="n">
-        <v>27.2938636578444</v>
+        <v>305.2160753980956</v>
       </c>
       <c r="H3" t="n">
-        <v>72.17266749628908</v>
+        <v>69.09808681934425</v>
       </c>
       <c r="I3" t="n">
-        <v>80.50014146258407</v>
+        <v>66.42225595059593</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -680,22 +680,22 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>18.67793333333333</v>
+        <v>345.6166666666667</v>
       </c>
       <c r="E4" t="n">
-        <v>29.6565</v>
+        <v>358.3974333333333</v>
       </c>
       <c r="F4" t="n">
-        <v>11.42391390088974</v>
+        <v>320.3395097107276</v>
       </c>
       <c r="G4" t="n">
-        <v>11.63657856259103</v>
+        <v>320.689018034049</v>
       </c>
       <c r="H4" t="n">
-        <v>55.44692920604529</v>
+        <v>64.61675662785962</v>
       </c>
       <c r="I4" t="n">
-        <v>59.58783215117909</v>
+        <v>59.67911560660773</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -920,22 +920,22 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>247.26765</v>
+        <v>299.5047</v>
       </c>
       <c r="E10" t="n">
-        <v>274.35</v>
+        <v>285.5666666666667</v>
       </c>
       <c r="F10" t="n">
-        <v>148.4081122812309</v>
+        <v>153.5348441515956</v>
       </c>
       <c r="G10" t="n">
-        <v>148.1693420519742</v>
+        <v>153.5526617847118</v>
       </c>
       <c r="H10" t="n">
-        <v>47.63775321159345</v>
+        <v>41.13690324412203</v>
       </c>
       <c r="I10" t="n">
-        <v>44.79805655414056</v>
+        <v>41.3531214666836</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
@@ -951,7 +951,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>D:\Hameeda_Projects\TAT_MS_INTERCITY\Data\Results\Paired\16-07-2026\PAIR_010_STRICT_Pondicherry_to_Chennai.xlsx</t>
+          <t>D:\Hameeda_Projects\TAT_MS_INTERCITY\Data\Results\Paired\15-07-2026_to_25-09-2026\PAIR_010_NONSTRICT_Chennai_to_Pondicherry.xlsx</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -960,22 +960,22 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>241.37365</v>
+        <v>247.26765</v>
       </c>
       <c r="E11" t="n">
-        <v>241.6157666666667</v>
+        <v>274.35</v>
       </c>
       <c r="F11" t="n">
-        <v>143.678327457659</v>
+        <v>148.4081122812309</v>
       </c>
       <c r="G11" t="n">
-        <v>143.7061031155876</v>
+        <v>148.1693420519742</v>
       </c>
       <c r="H11" t="n">
-        <v>44.63387255371435</v>
+        <v>47.63775321159345</v>
       </c>
       <c r="I11" t="n">
-        <v>42.34188357413701</v>
+        <v>44.79805655414056</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
@@ -991,7 +991,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>D:\Hameeda_Projects\TAT_MS_INTERCITY\Data\Results\Paired\16-07-2026_to_18-07-2026\PAIR_011_NONSTRICT_Pondicherry_to_Chennai.xlsx</t>
+          <t>D:\Hameeda_Projects\TAT_MS_INTERCITY\Data\Results\Paired\16-07-2026\PAIR_011_STRICT_Pondicherry_to_Chennai.xlsx</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1000,22 +1000,22 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>171.54615</v>
+        <v>241.37365</v>
       </c>
       <c r="E12" t="n">
-        <v>188.0674333333333</v>
+        <v>241.6157666666667</v>
       </c>
       <c r="F12" t="n">
-        <v>126.503272181271</v>
+        <v>143.678327457659</v>
       </c>
       <c r="G12" t="n">
-        <v>126.4504264596244</v>
+        <v>143.7061031155876</v>
       </c>
       <c r="H12" t="n">
-        <v>51.96681218238075</v>
+        <v>44.63387255371435</v>
       </c>
       <c r="I12" t="n">
-        <v>46.52364975832732</v>
+        <v>42.34188357413701</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
@@ -1040,22 +1040,22 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>183.89555</v>
+        <v>199.8837333333333</v>
       </c>
       <c r="E13" t="n">
-        <v>180.3055833333333</v>
+        <v>231.8833333333333</v>
       </c>
       <c r="F13" t="n">
-        <v>126.6046070482763</v>
+        <v>136.6906978560236</v>
       </c>
       <c r="G13" t="n">
-        <v>126.5641866441461</v>
+        <v>137.9070606846193</v>
       </c>
       <c r="H13" t="n">
-        <v>48.84353918109128</v>
+        <v>48.73228315978446</v>
       </c>
       <c r="I13" t="n">
-        <v>49.97551623726486</v>
+        <v>40.29552120062848</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -1071,7 +1071,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>D:\Hameeda_Projects\TAT_MS_INTERCITY\Data\Results\Paired\16-07-2026_to_20-07-2026\PAIR_013_NONSTRICT_Pondicherry_to_Chennai.xlsx</t>
+          <t>D:\Hameeda_Projects\TAT_MS_INTERCITY\Data\Results\Paired\16-07-2026_to_18-07-2026\PAIR_013_NONSTRICT_Pondicherry_to_Chennai.xlsx</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1080,22 +1080,22 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>205.7538833333333</v>
+        <v>251.7108833333333</v>
       </c>
       <c r="E14" t="n">
-        <v>194.9584</v>
+        <v>241.6157666666667</v>
       </c>
       <c r="F14" t="n">
-        <v>123.9185956857711</v>
+        <v>144.8690786295984</v>
       </c>
       <c r="G14" t="n">
-        <v>123.941936072907</v>
+        <v>143.7246699364842</v>
       </c>
       <c r="H14" t="n">
-        <v>44.92387297676966</v>
+        <v>40.96312925103651</v>
       </c>
       <c r="I14" t="n">
-        <v>42.76203218085404</v>
+        <v>42.34189937201894</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
@@ -1120,22 +1120,22 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>223.0419833333333</v>
+        <v>205.7538833333333</v>
       </c>
       <c r="E15" t="n">
-        <v>241.6157666666667</v>
+        <v>194.9584</v>
       </c>
       <c r="F15" t="n">
-        <v>143.715559613142</v>
+        <v>123.9185956857711</v>
       </c>
       <c r="G15" t="n">
-        <v>143.7030109884508</v>
+        <v>123.941936072907</v>
       </c>
       <c r="H15" t="n">
-        <v>46.2946098216972</v>
+        <v>44.92387297676966</v>
       </c>
       <c r="I15" t="n">
-        <v>42.3414520907443</v>
+        <v>42.76203218085404</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
@@ -1151,7 +1151,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>D:\Hameeda_Projects\TAT_MS_INTERCITY\Data\Results\Paired\16-07-2026_to_26-09-2026\PAIR_015_NONSTRICT_Pondicherry_to_Chennai.xlsx</t>
+          <t>D:\Hameeda_Projects\TAT_MS_INTERCITY\Data\Results\Paired\16-07-2026_to_20-07-2026\PAIR_015_NONSTRICT_Pondicherry_to_Chennai.xlsx</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1160,22 +1160,22 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>72.03223333333334</v>
+        <v>223.0419833333333</v>
       </c>
       <c r="E16" t="n">
-        <v>78.34408333333334</v>
+        <v>241.6157666666667</v>
       </c>
       <c r="F16" t="n">
-        <v>44.14952488525887</v>
+        <v>143.715559613142</v>
       </c>
       <c r="G16" t="n">
-        <v>44.09816148211158</v>
+        <v>143.7030109884508</v>
       </c>
       <c r="H16" t="n">
-        <v>49.19356496670422</v>
+        <v>46.2946098216972</v>
       </c>
       <c r="I16" t="n">
-        <v>48.98583197131639</v>
+        <v>42.3414520907443</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
@@ -1191,7 +1191,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>D:\Hameeda_Projects\TAT_MS_INTERCITY\Data\Results\Paired\17-07-2026\PAIR_016_STRICT_Chennai_to_Pondicherry.xlsx</t>
+          <t>D:\Hameeda_Projects\TAT_MS_INTERCITY\Data\Results\Paired\16-07-2026_to_26-09-2026\PAIR_016_NONSTRICT_Pondicherry_to_Chennai.xlsx</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1200,22 +1200,22 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>205.6434166666667</v>
+        <v>276.1022</v>
       </c>
       <c r="E17" t="n">
-        <v>221.15</v>
+        <v>291.3597166666667</v>
       </c>
       <c r="F17" t="n">
-        <v>141.5990549680233</v>
+        <v>152.2392917821083</v>
       </c>
       <c r="G17" t="n">
-        <v>141.6663057069586</v>
+        <v>153.9475902477031</v>
       </c>
       <c r="H17" t="n">
-        <v>51.08928882117495</v>
+        <v>40.35574549266031</v>
       </c>
       <c r="I17" t="n">
-        <v>44.82009341634151</v>
+        <v>36.02192303779674</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
@@ -1231,7 +1231,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>D:\Hameeda_Projects\TAT_MS_INTERCITY\Data\Results\Paired\17-07-2026_to_19-07-2026\PAIR_017_NONSTRICT_Chennai_to_Pondicherry.xlsx</t>
+          <t>D:\Hameeda_Projects\TAT_MS_INTERCITY\Data\Results\Paired\16-07-2026_to_26-09-2026\PAIR_017_NONSTRICT_Pondicherry_to_Chennai.xlsx</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1240,22 +1240,22 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>219.9365833333333</v>
+        <v>242.5876</v>
       </c>
       <c r="E18" t="n">
-        <v>269.2166666666666</v>
+        <v>242.5281833333333</v>
       </c>
       <c r="F18" t="n">
-        <v>146.1177802267258</v>
+        <v>145.5987620683535</v>
       </c>
       <c r="G18" t="n">
-        <v>146.2265476173816</v>
+        <v>143.8194371210736</v>
       </c>
       <c r="H18" t="n">
-        <v>48.97751792605069</v>
+        <v>44.70287136285296</v>
       </c>
       <c r="I18" t="n">
-        <v>44.8576416936978</v>
+        <v>42.18577398047646</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
@@ -1271,7 +1271,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>D:\Hameeda_Projects\TAT_MS_INTERCITY\Data\Results\Paired\17-07-2026_to_19-07-2026\PAIR_018_NONSTRICT_Chennai_to_Pondicherry.xlsx</t>
+          <t>D:\Hameeda_Projects\TAT_MS_INTERCITY\Data\Results\Paired\17-07-2026\PAIR_018_STRICT_Chennai_to_Pondicherry.xlsx</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1280,22 +1280,22 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>186.11555</v>
+        <v>205.6434166666667</v>
       </c>
       <c r="E19" t="n">
         <v>221.15</v>
       </c>
       <c r="F19" t="n">
-        <v>141.7178099447946</v>
+        <v>141.5990549680233</v>
       </c>
       <c r="G19" t="n">
-        <v>141.7137294264382</v>
+        <v>141.6663057069586</v>
       </c>
       <c r="H19" t="n">
-        <v>48.97984764694002</v>
+        <v>51.08928882117495</v>
       </c>
       <c r="I19" t="n">
-        <v>44.83512073701105</v>
+        <v>44.82009341634151</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
@@ -1311,7 +1311,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>D:\Hameeda_Projects\TAT_MS_INTERCITY\Data\Results\Paired\17-07-2026_to_25-09-2026\PAIR_019_NONSTRICT_Chennai_to_Pondicherry.xlsx</t>
+          <t>D:\Hameeda_Projects\TAT_MS_INTERCITY\Data\Results\Paired\17-07-2026_to_19-07-2026\PAIR_019_NONSTRICT_Chennai_to_Pondicherry.xlsx</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1320,22 +1320,22 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>221.1224333333333</v>
+        <v>219.9365833333333</v>
       </c>
       <c r="E20" t="n">
-        <v>221.15</v>
+        <v>269.2166666666666</v>
       </c>
       <c r="F20" t="n">
-        <v>141.8317368861638</v>
+        <v>146.1177802267258</v>
       </c>
       <c r="G20" t="n">
-        <v>141.6733980516045</v>
+        <v>146.2265476173816</v>
       </c>
       <c r="H20" t="n">
-        <v>49.27030586470386</v>
+        <v>48.97751792605069</v>
       </c>
       <c r="I20" t="n">
-        <v>44.82234079251659</v>
+        <v>44.8576416936978</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
@@ -1351,7 +1351,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>D:\Hameeda_Projects\TAT_MS_INTERCITY\Data\Results\Paired\18-07-2026\PAIR_020_STRICT_Pondicherry_to_Chennai.xlsx</t>
+          <t>D:\Hameeda_Projects\TAT_MS_INTERCITY\Data\Results\Paired\17-07-2026_to_19-07-2026\PAIR_020_NONSTRICT_Chennai_to_Pondicherry.xlsx</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1360,22 +1360,22 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>184.8726166666667</v>
+        <v>186.11555</v>
       </c>
       <c r="E21" t="n">
-        <v>189.8237333333333</v>
+        <v>221.15</v>
       </c>
       <c r="F21" t="n">
-        <v>126.797111280885</v>
+        <v>141.7178099447946</v>
       </c>
       <c r="G21" t="n">
-        <v>126.7676219192398</v>
+        <v>141.7137294264382</v>
       </c>
       <c r="H21" t="n">
-        <v>48.60919773277766</v>
+        <v>48.97984764694002</v>
       </c>
       <c r="I21" t="n">
-        <v>46.13403705248899</v>
+        <v>44.83512073701105</v>
       </c>
       <c r="J21" t="inlineStr">
         <is>
@@ -1391,7 +1391,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>D:\Hameeda_Projects\TAT_MS_INTERCITY\Data\Results\Paired\18-07-2026_to_20-07-2026\PAIR_021_NONSTRICT_Pondicherry_to_Chennai.xlsx</t>
+          <t>D:\Hameeda_Projects\TAT_MS_INTERCITY\Data\Results\Paired\17-07-2026_to_25-09-2026\PAIR_021_NONSTRICT_Chennai_to_Pondicherry.xlsx</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1400,22 +1400,22 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>139.3205333333333</v>
+        <v>235.7315</v>
       </c>
       <c r="E22" t="n">
-        <v>149.51085</v>
+        <v>285.5666666666667</v>
       </c>
       <c r="F22" t="n">
-        <v>106.7510397234517</v>
+        <v>153.5802936448807</v>
       </c>
       <c r="G22" t="n">
-        <v>106.7303536725813</v>
+        <v>153.5880362119665</v>
       </c>
       <c r="H22" t="n">
-        <v>51.58938782842431</v>
+        <v>47.72215002408557</v>
       </c>
       <c r="I22" t="n">
-        <v>49.91426587048593</v>
+        <v>41.36278147867761</v>
       </c>
       <c r="J22" t="inlineStr">
         <is>
@@ -1431,7 +1431,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>D:\Hameeda_Projects\TAT_MS_INTERCITY\Data\Results\Paired\18-07-2026_to_20-07-2026\PAIR_022_NONSTRICT_Pondicherry_to_Chennai.xlsx</t>
+          <t>D:\Hameeda_Projects\TAT_MS_INTERCITY\Data\Results\Paired\17-07-2026_to_25-09-2026\PAIR_022_NONSTRICT_Chennai_to_Pondicherry.xlsx</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1440,22 +1440,22 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>166.3452166666667</v>
+        <v>221.1224333333333</v>
       </c>
       <c r="E23" t="n">
-        <v>188.0674333333333</v>
+        <v>221.15</v>
       </c>
       <c r="F23" t="n">
-        <v>126.5111630773044</v>
+        <v>141.8317368861638</v>
       </c>
       <c r="G23" t="n">
-        <v>126.4609732010443</v>
+        <v>141.6733980516045</v>
       </c>
       <c r="H23" t="n">
-        <v>54.3571101011709</v>
+        <v>49.27030586470386</v>
       </c>
       <c r="I23" t="n">
-        <v>46.52817854574852</v>
+        <v>44.82234079251659</v>
       </c>
       <c r="J23" t="inlineStr">
         <is>
@@ -1471,7 +1471,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>D:\Hameeda_Projects\TAT_MS_INTERCITY\Data\Results\Paired\18-07-2026_to_26-09-2026\PAIR_023_NONSTRICT_Pondicherry_to_Chennai.xlsx</t>
+          <t>D:\Hameeda_Projects\TAT_MS_INTERCITY\Data\Results\Paired\18-07-2026\PAIR_023_STRICT_Pondicherry_to_Chennai.xlsx</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1480,22 +1480,22 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>72.03223333333334</v>
+        <v>223.05115</v>
       </c>
       <c r="E24" t="n">
-        <v>81.07328333333334</v>
+        <v>231.8833333333333</v>
       </c>
       <c r="F24" t="n">
-        <v>44.14425672881129</v>
+        <v>137.8478512787692</v>
       </c>
       <c r="G24" t="n">
-        <v>44.07790624114242</v>
+        <v>137.9112374368539</v>
       </c>
       <c r="H24" t="n">
-        <v>49.18766031137466</v>
+        <v>43.48920820013006</v>
       </c>
       <c r="I24" t="n">
-        <v>46.38866788428458</v>
+        <v>40.29129762507425</v>
       </c>
       <c r="J24" t="inlineStr">
         <is>
@@ -1511,7 +1511,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>D:\Hameeda_Projects\TAT_MS_INTERCITY\Data\Results\Paired\19-07-2026\PAIR_024_STRICT_Chennai_to_Pondicherry.xlsx</t>
+          <t>D:\Hameeda_Projects\TAT_MS_INTERCITY\Data\Results\Paired\18-07-2026_to_20-07-2026\PAIR_024_NONSTRICT_Pondicherry_to_Chennai.xlsx</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1520,22 +1520,22 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>195.4022</v>
+        <v>207.1358666666667</v>
       </c>
       <c r="E25" t="n">
-        <v>266.8632166666667</v>
+        <v>194.5326</v>
       </c>
       <c r="F25" t="n">
-        <v>145.9064422742808</v>
+        <v>125.021511754306</v>
       </c>
       <c r="G25" t="n">
-        <v>145.9943306994593</v>
+        <v>123.8871365945718</v>
       </c>
       <c r="H25" t="n">
-        <v>48.03268705989514</v>
+        <v>41.52158885696085</v>
       </c>
       <c r="I25" t="n">
-        <v>45.34276468747346</v>
+        <v>42.83521220753777</v>
       </c>
       <c r="J25" t="inlineStr">
         <is>
@@ -1551,7 +1551,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>D:\Hameeda_Projects\TAT_MS_INTERCITY\Data\Results\Paired\19-07-2026_to_25-09-2026\PAIR_025_NONSTRICT_Chennai_to_Pondicherry.xlsx</t>
+          <t>D:\Hameeda_Projects\TAT_MS_INTERCITY\Data\Results\Paired\18-07-2026_to_20-07-2026\PAIR_025_NONSTRICT_Pondicherry_to_Chennai.xlsx</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1560,22 +1560,22 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>255.7438833333333</v>
+        <v>189.99105</v>
       </c>
       <c r="E26" t="n">
-        <v>265.6299833333333</v>
+        <v>231.8833333333333</v>
       </c>
       <c r="F26" t="n">
-        <v>145.9773325040056</v>
+        <v>136.7168885797278</v>
       </c>
       <c r="G26" t="n">
-        <v>145.8893363990339</v>
+        <v>137.9082545861779</v>
       </c>
       <c r="H26" t="n">
-        <v>47.2452299004206</v>
+        <v>50.21471932710446</v>
       </c>
       <c r="I26" t="n">
-        <v>45.59497163487288</v>
+        <v>40.29636713820891</v>
       </c>
       <c r="J26" t="inlineStr">
         <is>
@@ -1591,7 +1591,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>D:\Hameeda_Projects\TAT_MS_INTERCITY\Data\Results\Paired\20-07-2026\PAIR_026_STRICT_Pondicherry_to_Chennai.xlsx</t>
+          <t>D:\Hameeda_Projects\TAT_MS_INTERCITY\Data\Results\Paired\18-07-2026_to_26-09-2026\PAIR_026_NONSTRICT_Pondicherry_to_Chennai.xlsx</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1600,22 +1600,22 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>187.65295</v>
+        <v>281.0869</v>
       </c>
       <c r="E27" t="n">
-        <v>194.9584</v>
+        <v>291.75</v>
       </c>
       <c r="F27" t="n">
-        <v>123.9926446469637</v>
+        <v>153.3729275658394</v>
       </c>
       <c r="G27" t="n">
-        <v>123.9802750677086</v>
+        <v>154.0634351764531</v>
       </c>
       <c r="H27" t="n">
-        <v>46.88285886366883</v>
+        <v>38.12896580160068</v>
       </c>
       <c r="I27" t="n">
-        <v>42.76169445348732</v>
+        <v>35.98974180825657</v>
       </c>
       <c r="J27" t="inlineStr">
         <is>
@@ -1631,7 +1631,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>D:\Hameeda_Projects\TAT_MS_INTERCITY\Data\Results\Paired\20-07-2026_to_29-07-2026\PAIR_027_NONSTRICT_SilkBoard_to_Madhuravoyal.xlsx</t>
+          <t>D:\Hameeda_Projects\TAT_MS_INTERCITY\Data\Results\Paired\18-07-2026_to_26-09-2026\PAIR_027_NONSTRICT_Pondicherry_to_Chennai.xlsx</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1640,22 +1640,22 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>39.97585</v>
+        <v>219.9088</v>
       </c>
       <c r="E28" t="n">
-        <v>23.74308333333333</v>
+        <v>231.8833333333333</v>
       </c>
       <c r="F28" t="n">
-        <v>14.82892455320712</v>
+        <v>138.2944646000696</v>
       </c>
       <c r="G28" t="n">
-        <v>15.14287648205564</v>
+        <v>137.8693466671948</v>
       </c>
       <c r="H28" t="n">
-        <v>57.87321624947242</v>
+        <v>46.48372876031184</v>
       </c>
       <c r="I28" t="n">
-        <v>38.26683233039817</v>
+        <v>40.28662307790311</v>
       </c>
       <c r="J28" t="inlineStr">
         <is>
@@ -1671,7 +1671,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>D:\Hameeda_Projects\TAT_MS_INTERCITY\Data\Results\Paired\20-07-2026_to_05-09-2026\PAIR_028_NONSTRICT_SilkBoard_to_Madhuravoyal.xlsx</t>
+          <t>D:\Hameeda_Projects\TAT_MS_INTERCITY\Data\Results\Paired\19-07-2026\PAIR_028_STRICT_Chennai_to_Pondicherry.xlsx</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1680,22 +1680,22 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>20.26271666666667</v>
+        <v>195.4022</v>
       </c>
       <c r="E29" t="n">
-        <v>19.8356</v>
+        <v>266.8632166666667</v>
       </c>
       <c r="F29" t="n">
-        <v>22.49736924506911</v>
+        <v>145.9064422742808</v>
       </c>
       <c r="G29" t="n">
-        <v>22.45363674285612</v>
+        <v>145.9943306994593</v>
       </c>
       <c r="H29" t="n">
-        <v>71.17338391598146</v>
+        <v>48.03268705989514</v>
       </c>
       <c r="I29" t="n">
-        <v>67.91920610273282</v>
+        <v>45.34276468747346</v>
       </c>
       <c r="J29" t="inlineStr">
         <is>
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>D:\Hameeda_Projects\TAT_MS_INTERCITY\Data\Results\Paired\20-07-2026_to_26-09-2026\PAIR_029_NONSTRICT_Pondicherry_to_Chennai.xlsx</t>
+          <t>D:\Hameeda_Projects\TAT_MS_INTERCITY\Data\Results\Paired\19-07-2026_to_25-09-2026\PAIR_029_NONSTRICT_Chennai_to_Pondicherry.xlsx</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1720,22 +1720,22 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>42.85905</v>
+        <v>202.4542833333333</v>
       </c>
       <c r="E30" t="n">
-        <v>45.4903</v>
+        <v>266.7375833333334</v>
       </c>
       <c r="F30" t="n">
-        <v>34.43958194459641</v>
+        <v>148.6184563331109</v>
       </c>
       <c r="G30" t="n">
-        <v>34.32677600023323</v>
+        <v>148.5522231625584</v>
       </c>
       <c r="H30" t="n">
-        <v>49.88240215190034</v>
+        <v>47.68589618099658</v>
       </c>
       <c r="I30" t="n">
-        <v>45.25609711599014</v>
+        <v>42.94452978486028</v>
       </c>
       <c r="J30" t="inlineStr">
         <is>
@@ -1751,7 +1751,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>D:\Hameeda_Projects\TAT_MS_INTERCITY\Data\Results\Paired\29-07-2026_to_06-09-2026\PAIR_030_NONSTRICT_SilkBoard_to_Madhuravoyal.xlsx</t>
+          <t>D:\Hameeda_Projects\TAT_MS_INTERCITY\Data\Results\Paired\19-07-2026_to_25-09-2026\PAIR_030_NONSTRICT_Chennai_to_Pondicherry.xlsx</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1760,22 +1760,22 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>231.7772166666667</v>
+        <v>255.7438833333333</v>
       </c>
       <c r="E31" t="n">
-        <v>213.89885</v>
+        <v>265.6299833333333</v>
       </c>
       <c r="F31" t="n">
-        <v>231.4242273523428</v>
+        <v>145.9773325040056</v>
       </c>
       <c r="G31" t="n">
-        <v>231.3323956071126</v>
+        <v>145.8893363990339</v>
       </c>
       <c r="H31" t="n">
-        <v>67.59910743007244</v>
+        <v>47.2452299004206</v>
       </c>
       <c r="I31" t="n">
-        <v>70.84744357406082</v>
+        <v>45.59497163487288</v>
       </c>
       <c r="J31" t="inlineStr">
         <is>
@@ -1791,7 +1791,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>D:\Hameeda_Projects\TAT_MS_INTERCITY\Data\Results\Paired\31-07-2026_to_04-09-2026\PAIR_031_NONSTRICT_Madhuravoyal_to_SilkBoard.xlsx</t>
+          <t>D:\Hameeda_Projects\TAT_MS_INTERCITY\Data\Results\Paired\20-07-2026\PAIR_031_STRICT_Pondicherry_to_Chennai.xlsx</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1800,22 +1800,22 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>14.8788</v>
+        <v>187.65295</v>
       </c>
       <c r="E32" t="n">
-        <v>16.75645</v>
+        <v>194.9584</v>
       </c>
       <c r="F32" t="n">
-        <v>12.73848083938423</v>
+        <v>123.9926446469637</v>
       </c>
       <c r="G32" t="n">
-        <v>12.6496249595659</v>
+        <v>123.9802750677086</v>
       </c>
       <c r="H32" t="n">
-        <v>51.36898475435208</v>
+        <v>46.88285886366883</v>
       </c>
       <c r="I32" t="n">
-        <v>45.29464758788131</v>
+        <v>42.76169445348732</v>
       </c>
       <c r="J32" t="inlineStr">
         <is>
@@ -1831,7 +1831,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>D:\Hameeda_Projects\TAT_MS_INTERCITY\Data\Results\Paired\05-09-2026_to_06-09-2026\PAIR_032_STRICT_SilkBoard_to_Madhuravoyal.xlsx</t>
+          <t>D:\Hameeda_Projects\TAT_MS_INTERCITY\Data\Results\Paired\20-07-2026_to_29-07-2026\PAIR_032_NONSTRICT_SilkBoard_to_Madhuravoyal.xlsx</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1840,22 +1840,22 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>251.8893</v>
+        <v>356.1224666666666</v>
       </c>
       <c r="E33" t="n">
-        <v>234.6249833333333</v>
+        <v>333.4333333333333</v>
       </c>
       <c r="F33" t="n">
-        <v>240.4425765887812</v>
+        <v>324.8278468558257</v>
       </c>
       <c r="G33" t="n">
-        <v>240.7230050078111</v>
+        <v>330.6538536572841</v>
       </c>
       <c r="H33" t="n">
-        <v>64.24069875201077</v>
+        <v>65.68858194612334</v>
       </c>
       <c r="I33" t="n">
-        <v>68.13871680530009</v>
+        <v>62.88775311063549</v>
       </c>
       <c r="J33" t="inlineStr">
         <is>
@@ -1871,7 +1871,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>D:\Hameeda_Projects\TAT_MS_INTERCITY\Data\Results\Paired\11-09-2026\PAIR_033_STRICT_Madhuravoyal_to_Madiwala.xlsx</t>
+          <t>D:\Hameeda_Projects\TAT_MS_INTERCITY\Data\Results\Paired\20-07-2026_to_05-09-2026\PAIR_033_NONSTRICT_SilkBoard_to_Madhuravoyal.xlsx</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1880,22 +1880,22 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>184.8808833333333</v>
+        <v>350.0545666666667</v>
       </c>
       <c r="E34" t="n">
-        <v>189.0966166666667</v>
+        <v>317.3162</v>
       </c>
       <c r="F34" t="n">
-        <v>159.8172074707595</v>
+        <v>320.295003456412</v>
       </c>
       <c r="G34" t="n">
-        <v>159.58380997156</v>
+        <v>320.9302329433269</v>
       </c>
       <c r="H34" t="n">
-        <v>58.20216621959079</v>
+        <v>66.1266599366777</v>
       </c>
       <c r="I34" t="n">
-        <v>55.92805804691302</v>
+        <v>65.88396841768795</v>
       </c>
       <c r="J34" t="inlineStr">
         <is>
@@ -1911,7 +1911,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>D:\Hameeda_Projects\TAT_MS_INTERCITY\Data\Results\Paired\11-09-2026_to_18-09-2026\PAIR_034_NONSTRICT_Madhuravoyal_to_Madiwala.xlsx</t>
+          <t>D:\Hameeda_Projects\TAT_MS_INTERCITY\Data\Results\Paired\20-07-2026_to_26-09-2026\PAIR_034_NONSTRICT_Pondicherry_to_Chennai.xlsx</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1920,22 +1920,22 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>66.01939999999999</v>
+        <v>252.8470333333333</v>
       </c>
       <c r="E35" t="n">
-        <v>94.14933333333333</v>
+        <v>291.75</v>
       </c>
       <c r="F35" t="n">
-        <v>49.09342708546251</v>
+        <v>152.3946794802466</v>
       </c>
       <c r="G35" t="n">
-        <v>49.01363547616007</v>
+        <v>154.0323598514136</v>
       </c>
       <c r="H35" t="n">
-        <v>47.58550177729312</v>
+        <v>42.28793493991633</v>
       </c>
       <c r="I35" t="n">
-        <v>37.18511343393678</v>
+        <v>35.98718333260023</v>
       </c>
       <c r="J35" t="inlineStr">
         <is>
@@ -1951,7 +1951,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>D:\Hameeda_Projects\TAT_MS_INTERCITY\Data\Results\Paired\12-09-2026\PAIR_035_STRICT_Madiwala_to_Madhuravoyal.xlsx</t>
+          <t>D:\Hameeda_Projects\TAT_MS_INTERCITY\Data\Results\Paired\20-07-2026_to_26-09-2026\PAIR_035_NONSTRICT_Pondicherry_to_Chennai.xlsx</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1960,22 +1960,22 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>13.15565</v>
+        <v>194.9381166666667</v>
       </c>
       <c r="E36" t="n">
-        <v>14.03436666666667</v>
+        <v>194.9584</v>
       </c>
       <c r="F36" t="n">
-        <v>17.5104260598227</v>
+        <v>125.7416693023907</v>
       </c>
       <c r="G36" t="n">
-        <v>17.59592292311513</v>
+        <v>123.9823800042885</v>
       </c>
       <c r="H36" t="n">
-        <v>79.86116714790693</v>
+        <v>45.47510257059169</v>
       </c>
       <c r="I36" t="n">
-        <v>75.22643525442838</v>
+        <v>42.7689234538736</v>
       </c>
       <c r="J36" t="inlineStr">
         <is>
@@ -1991,7 +1991,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>D:\Hameeda_Projects\TAT_MS_INTERCITY\Data\Results\Paired\12-09-2026_to_20-09-2026\PAIR_036_NONSTRICT_Madiwala_to_Madhuravoyal.xlsx</t>
+          <t>D:\Hameeda_Projects\TAT_MS_INTERCITY\Data\Results\Paired\31-07-2026_to_04-09-2026\PAIR_036_NONSTRICT_Madhuravoyal_to_SilkBoard.xlsx</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2000,22 +2000,22 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>11.71183333333333</v>
+        <v>477.62115</v>
       </c>
       <c r="E37" t="n">
-        <v>11.73173333333333</v>
+        <v>368.0833333333333</v>
       </c>
       <c r="F37" t="n">
-        <v>16.43424965629278</v>
+        <v>326.4581126643001</v>
       </c>
       <c r="G37" t="n">
-        <v>16.43868693033036</v>
+        <v>326.5906174282528</v>
       </c>
       <c r="H37" t="n">
-        <v>84.19305084978724</v>
+        <v>53.20517022732241</v>
       </c>
       <c r="I37" t="n">
-        <v>84.07293174806406</v>
+        <v>59.00405914179443</v>
       </c>
       <c r="J37" t="inlineStr">
         <is>
@@ -2031,7 +2031,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>D:\Hameeda_Projects\TAT_MS_INTERCITY\Data\Results\Paired\12-09-2026_to_20-09-2026\PAIR_037_NONSTRICT_Madiwala_to_Madhuravoyal.xlsx</t>
+          <t>D:\Hameeda_Projects\TAT_MS_INTERCITY\Data\Results\Paired\05-09-2026_to_06-09-2026\PAIR_037_STRICT_SilkBoard_to_Madhuravoyal.xlsx</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2040,22 +2040,22 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>116.7043666666667</v>
+        <v>261.38705</v>
       </c>
       <c r="E38" t="n">
-        <v>117.7956</v>
+        <v>244.9409666666667</v>
       </c>
       <c r="F38" t="n">
-        <v>106.4407237351212</v>
+        <v>249.1268483717951</v>
       </c>
       <c r="G38" t="n">
-        <v>106.429493371315</v>
+        <v>249.9072012121763</v>
       </c>
       <c r="H38" t="n">
-        <v>57.74313792935574</v>
+        <v>63.84368844822295</v>
       </c>
       <c r="I38" t="n">
-        <v>61.22560386453947</v>
+        <v>67.45522324597772</v>
       </c>
       <c r="J38" t="inlineStr">
         <is>
@@ -2071,7 +2071,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>D:\Hameeda_Projects\TAT_MS_INTERCITY\Data\Results\Paired\20-09-2026\PAIR_038_STRICT_Madiwala_to_Madhuravoyal.xlsx</t>
+          <t>D:\Hameeda_Projects\TAT_MS_INTERCITY\Data\Results\Paired\11-09-2026\PAIR_038_STRICT_Madhuravoyal_to_Madiwala.xlsx</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2080,24 +2080,664 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>154.2935833333334</v>
+        <v>395</v>
       </c>
       <c r="E39" t="n">
-        <v>89.89455</v>
+        <v>374.9615166666666</v>
       </c>
       <c r="F39" t="n">
-        <v>118.6528555237152</v>
+        <v>326.3547725745892</v>
       </c>
       <c r="G39" t="n">
-        <v>118.3205529638225</v>
+        <v>325.9460971942599</v>
       </c>
       <c r="H39" t="n">
-        <v>76.62526023529979</v>
+        <v>61.31623721877904</v>
       </c>
       <c r="I39" t="n">
-        <v>78.97289855535573</v>
+        <v>59.54001701508474</v>
       </c>
       <c r="J39" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>PAIR_039</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>D:\Hameeda_Projects\TAT_MS_INTERCITY\Data\Results\Paired\11-09-2026_to_18-09-2026\PAIR_039_NONSTRICT_Madhuravoyal_to_Madiwala.xlsx</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>392.3709333333334</v>
+      </c>
+      <c r="E40" t="n">
+        <v>411.8826166666667</v>
+      </c>
+      <c r="F40" t="n">
+        <v>325.4159138009351</v>
+      </c>
+      <c r="G40" t="n">
+        <v>325.0535176750399</v>
+      </c>
+      <c r="H40" t="n">
+        <v>61.64781186469645</v>
+      </c>
+      <c r="I40" t="n">
+        <v>56.977909507314</v>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>PAIR_040</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>D:\Hameeda_Projects\TAT_MS_INTERCITY\Data\Results\Paired\11-09-2026_to_02-10-2026\PAIR_040_NONSTRICT_Madhuravoyal_to_Madiwala.xlsx</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>395</v>
+      </c>
+      <c r="E41" t="n">
+        <v>319.5048166666667</v>
+      </c>
+      <c r="F41" t="n">
+        <v>326.4235517768342</v>
+      </c>
+      <c r="G41" t="n">
+        <v>325.9521091087573</v>
+      </c>
+      <c r="H41" t="n">
+        <v>61.32917712617816</v>
+      </c>
+      <c r="I41" t="n">
+        <v>62.63705094403212</v>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>PAIR_041</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>D:\Hameeda_Projects\TAT_MS_INTERCITY\Data\Results\Paired\11-09-2026_to_02-10-2026\PAIR_041_NONSTRICT_Madhuravoyal_to_Madiwala.xlsx</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>353.84785</v>
+      </c>
+      <c r="E42" t="n">
+        <v>372.5504</v>
+      </c>
+      <c r="F42" t="n">
+        <v>325.4492993959398</v>
+      </c>
+      <c r="G42" t="n">
+        <v>325.1974783974341</v>
+      </c>
+      <c r="H42" t="n">
+        <v>67.12149214202077</v>
+      </c>
+      <c r="I42" t="n">
+        <v>59.84310713127186</v>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>PAIR_042</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>D:\Hameeda_Projects\TAT_MS_INTERCITY\Data\Results\Paired\12-09-2026\PAIR_042_STRICT_Madiwala_to_Madhuravoyal.xlsx</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>405.7706333333333</v>
+      </c>
+      <c r="E43" t="n">
+        <v>325.4048166666667</v>
+      </c>
+      <c r="F43" t="n">
+        <v>321.8611957625617</v>
+      </c>
+      <c r="G43" t="n">
+        <v>322.4334194047157</v>
+      </c>
+      <c r="H43" t="n">
+        <v>64.64531488636605</v>
+      </c>
+      <c r="I43" t="n">
+        <v>63.96489623843365</v>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>PAIR_043</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>D:\Hameeda_Projects\TAT_MS_INTERCITY\Data\Results\Paired\12-09-2026_to_20-09-2026\PAIR_043_NONSTRICT_Madiwala_to_Madhuravoyal.xlsx</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>446.45</v>
+      </c>
+      <c r="E44" t="n">
+        <v>341.4423833333333</v>
+      </c>
+      <c r="F44" t="n">
+        <v>322.1774743037008</v>
+      </c>
+      <c r="G44" t="n">
+        <v>321.6269481176106</v>
+      </c>
+      <c r="H44" t="n">
+        <v>64.4401967523076</v>
+      </c>
+      <c r="I44" t="n">
+        <v>64.28145295102571</v>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>PAIR_044</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>D:\Hameeda_Projects\TAT_MS_INTERCITY\Data\Results\Paired\12-09-2026_to_20-09-2026\PAIR_044_NONSTRICT_Madiwala_to_Madhuravoyal.xlsx</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>408.6267666666666</v>
+      </c>
+      <c r="E45" t="n">
+        <v>325.2655</v>
+      </c>
+      <c r="F45" t="n">
+        <v>324.4297883243897</v>
+      </c>
+      <c r="G45" t="n">
+        <v>325.0350667285441</v>
+      </c>
+      <c r="H45" t="n">
+        <v>62.28065772239027</v>
+      </c>
+      <c r="I45" t="n">
+        <v>63.75914065702941</v>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>PAIR_045</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>D:\Hameeda_Projects\TAT_MS_INTERCITY\Data\Results\Paired\12-09-2026_to_03-10-2026\PAIR_045_NONSTRICT_Madiwala_to_Madhuravoyal.xlsx</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>446.45</v>
+      </c>
+      <c r="E46" t="n">
+        <v>349.4259833333334</v>
+      </c>
+      <c r="F46" t="n">
+        <v>322.2735940834601</v>
+      </c>
+      <c r="G46" t="n">
+        <v>322.6469826189222</v>
+      </c>
+      <c r="H46" t="n">
+        <v>64.45944316240457</v>
+      </c>
+      <c r="I46" t="n">
+        <v>59.87583735700611</v>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>PAIR_046</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>D:\Hameeda_Projects\TAT_MS_INTERCITY\Data\Results\Paired\12-09-2026_to_03-10-2026\PAIR_046_NONSTRICT_Madiwala_to_Madhuravoyal.xlsx</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>394.6350333333333</v>
+      </c>
+      <c r="E47" t="n">
+        <v>329.75</v>
+      </c>
+      <c r="F47" t="n">
+        <v>324.9350283808783</v>
+      </c>
+      <c r="G47" t="n">
+        <v>325.7263480402497</v>
+      </c>
+      <c r="H47" t="n">
+        <v>64.17415185678969</v>
+      </c>
+      <c r="I47" t="n">
+        <v>63.70255625065911</v>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>PAIR_047</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>D:\Hameeda_Projects\TAT_MS_INTERCITY\Data\Results\Paired\18-09-2026_to_02-10-2026\PAIR_047_NONSTRICT_Madhuravoyal_to_Madiwala.xlsx</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>353.84785</v>
+      </c>
+      <c r="E48" t="n">
+        <v>412.4881333333333</v>
+      </c>
+      <c r="F48" t="n">
+        <v>325.3816512944114</v>
+      </c>
+      <c r="G48" t="n">
+        <v>325.1731293793417</v>
+      </c>
+      <c r="H48" t="n">
+        <v>67.10753118315435</v>
+      </c>
+      <c r="I48" t="n">
+        <v>57.06712981492286</v>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>PAIR_048</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>D:\Hameeda_Projects\TAT_MS_INTERCITY\Data\Results\Paired\20-09-2026\PAIR_048_STRICT_Madiwala_to_Madhuravoyal.xlsx</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>410.7333333333333</v>
+      </c>
+      <c r="E49" t="n">
+        <v>348.1472000000001</v>
+      </c>
+      <c r="F49" t="n">
+        <v>325.3989070955062</v>
+      </c>
+      <c r="G49" t="n">
+        <v>324.8843224200924</v>
+      </c>
+      <c r="H49" t="n">
+        <v>62.04817090988592</v>
+      </c>
+      <c r="I49" t="n">
+        <v>63.51275377345894</v>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>PAIR_049</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>D:\Hameeda_Projects\TAT_MS_INTERCITY\Data\Results\Paired\20-09-2026_to_03-10-2026\PAIR_049_NONSTRICT_Madiwala_to_Madhuravoyal.xlsx</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>407.74795</v>
+      </c>
+      <c r="E50" t="n">
+        <v>346.04665</v>
+      </c>
+      <c r="F50" t="n">
+        <v>323.753642085549</v>
+      </c>
+      <c r="G50" t="n">
+        <v>324.1251397273161</v>
+      </c>
+      <c r="H50" t="n">
+        <v>62.32616891116043</v>
+      </c>
+      <c r="I50" t="n">
+        <v>60.09883681712126</v>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>PAIR_050</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>D:\Hameeda_Projects\TAT_MS_INTERCITY\Data\Results\Paired\20-09-2026_to_03-10-2026\PAIR_050_NONSTRICT_Madiwala_to_Madhuravoyal.xlsx</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>420.64665</v>
+      </c>
+      <c r="E51" t="n">
+        <v>351.75</v>
+      </c>
+      <c r="F51" t="n">
+        <v>326.4659622430934</v>
+      </c>
+      <c r="G51" t="n">
+        <v>326.1341423944449</v>
+      </c>
+      <c r="H51" t="n">
+        <v>63.92417977688259</v>
+      </c>
+      <c r="I51" t="n">
+        <v>63.01656664035327</v>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>PAIR_051</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>D:\Hameeda_Projects\TAT_MS_INTERCITY\Data\Results\Paired\25-09-2026\PAIR_051_STRICT_Chennai_to_Pondicherry.xlsx</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>265.8149333333333</v>
+      </c>
+      <c r="E52" t="n">
+        <v>285.5666666666667</v>
+      </c>
+      <c r="F52" t="n">
+        <v>153.6764767050815</v>
+      </c>
+      <c r="G52" t="n">
+        <v>153.5307402784298</v>
+      </c>
+      <c r="H52" t="n">
+        <v>45.91137366592437</v>
+      </c>
+      <c r="I52" t="n">
+        <v>41.34713516442955</v>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>PAIR_052</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>D:\Hameeda_Projects\TAT_MS_INTERCITY\Data\Results\Paired\26-09-2026\PAIR_052_STRICT_Pondicherry_to_Chennai.xlsx</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>263.95295</v>
+      </c>
+      <c r="E53" t="n">
+        <v>286.3403666666666</v>
+      </c>
+      <c r="F53" t="n">
+        <v>151.560156776244</v>
+      </c>
+      <c r="G53" t="n">
+        <v>152.1093053055016</v>
+      </c>
+      <c r="H53" t="n">
+        <v>42.41012053032751</v>
+      </c>
+      <c r="I53" t="n">
+        <v>36.29360732288521</v>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>PAIR_053</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>D:\Hameeda_Projects\TAT_MS_INTERCITY\Data\Results\Paired\02-10-2026\PAIR_053_STRICT_Madhuravoyal_to_Madiwala.xlsx</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>353.84785</v>
+      </c>
+      <c r="E54" t="n">
+        <v>317.9467666666667</v>
+      </c>
+      <c r="F54" t="n">
+        <v>325.4090582064992</v>
+      </c>
+      <c r="G54" t="n">
+        <v>325.0956316318464</v>
+      </c>
+      <c r="H54" t="n">
+        <v>67.11318731782285</v>
+      </c>
+      <c r="I54" t="n">
+        <v>62.7857905819767</v>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>PAIR_054</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>D:\Hameeda_Projects\TAT_MS_INTERCITY\Data\Results\Paired\03-10-2026\PAIR_054_STRICT_Madiwala_to_Madhuravoyal.xlsx</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>417.3654666666667</v>
+      </c>
+      <c r="E55" t="n">
+        <v>352.7333333333333</v>
+      </c>
+      <c r="F55" t="n">
+        <v>324.469507401836</v>
+      </c>
+      <c r="G55" t="n">
+        <v>325.0334484112802</v>
+      </c>
+      <c r="H55" t="n">
+        <v>64.21541291915878</v>
+      </c>
+      <c r="I55" t="n">
+        <v>59.70765591182442</v>
+      </c>
+      <c r="J55" t="inlineStr">
         <is>
           <t>NONE</t>
         </is>
